--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122193935</v>
       </c>
       <c r="B2" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122193935</v>
       </c>
       <c r="B2" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,240 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129486827</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92827</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>471288</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6544011</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4 st f.k</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129487544</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92827</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>471291</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6544233</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>14 st f.k</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,6 +1022,118 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129572834</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>471271</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6544243</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>129572834</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>129572834</v>
       </c>
       <c r="B5" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>129572834</v>
       </c>
       <c r="B5" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129486827</v>
       </c>
       <c r="B3" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129487544</v>
       </c>
       <c r="B4" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>129572834</v>
       </c>
       <c r="B5" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>129572834</v>
       </c>
       <c r="B5" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,6 +1135,1052 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131338442</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>471280</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6543893</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre födohack vid basen på lutande död tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131338050</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>471297</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6543926</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnag och kläckhål på stående död gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131338964</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>471288</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6544000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skrämdes upp och flög nordväst.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131339176</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>471314</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6544075</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av döende gran.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131338393</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>471301</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6543890</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen på död stående tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131338884</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57073</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>471264</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6543968</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På 2 stenar.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131339035</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>471304</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6544023</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre födohack vid basen av död stående tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131337775</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>471285</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6543973</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska födohack på låga av tall.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131337729</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57073</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>471298</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6543979</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131338884</v>
+        <v>131337775</v>
       </c>
       <c r="B11" t="n">
-        <v>57073</v>
+        <v>57881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471264</v>
+        <v>471285</v>
       </c>
       <c r="R11" t="n">
-        <v>6543968</v>
+        <v>6543973</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131337775</v>
+        <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>57073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471285</v>
+        <v>471264</v>
       </c>
       <c r="R13" t="n">
-        <v>6543973</v>
+        <v>6543968</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>131338964</v>
       </c>
       <c r="B8" t="n">
-        <v>57076</v>
+        <v>57078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R11" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131339035</v>
+        <v>131337775</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471304</v>
+        <v>471285</v>
       </c>
       <c r="R12" t="n">
-        <v>6544023</v>
+        <v>6543973</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1957,7 @@
         <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>131337729</v>
       </c>
       <c r="B14" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>131338964</v>
       </c>
       <c r="B8" t="n">
-        <v>57078</v>
+        <v>57079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131339035</v>
+        <v>131337775</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471304</v>
+        <v>471285</v>
       </c>
       <c r="R11" t="n">
-        <v>6544023</v>
+        <v>6543973</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R12" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1957,7 @@
         <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>131337729</v>
       </c>
       <c r="B14" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1751,7 +1751,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R11" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,7 +1837,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131339035</v>
+        <v>131337775</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471304</v>
+        <v>471285</v>
       </c>
       <c r="R12" t="n">
-        <v>6544023</v>
+        <v>6543973</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2181,6 +2181,230 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131444818</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>471258</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6544133</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre gnag på låga av björk.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131444592</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>471273</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6544232</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131339035</v>
+        <v>131338884</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471304</v>
+        <v>471264</v>
       </c>
       <c r="R11" t="n">
-        <v>6544023</v>
+        <v>6543968</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131338884</v>
+        <v>131339035</v>
       </c>
       <c r="B13" t="n">
-        <v>57076</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471264</v>
+        <v>471304</v>
       </c>
       <c r="R13" t="n">
-        <v>6543968</v>
+        <v>6544023</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131338884</v>
+        <v>131337775</v>
       </c>
       <c r="B11" t="n">
-        <v>57076</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471264</v>
+        <v>471285</v>
       </c>
       <c r="R11" t="n">
-        <v>6543968</v>
+        <v>6543973</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R12" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131339035</v>
+        <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471304</v>
+        <v>471264</v>
       </c>
       <c r="R13" t="n">
-        <v>6544023</v>
+        <v>6543968</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131337775</v>
+        <v>131338884</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471285</v>
+        <v>471264</v>
       </c>
       <c r="R11" t="n">
-        <v>6543973</v>
+        <v>6543968</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,7 +1837,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131339035</v>
+        <v>131337775</v>
       </c>
       <c r="B12" t="n">
         <v>57885</v>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471304</v>
+        <v>471285</v>
       </c>
       <c r="R12" t="n">
-        <v>6544023</v>
+        <v>6543973</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131338884</v>
+        <v>131339035</v>
       </c>
       <c r="B13" t="n">
-        <v>57076</v>
+        <v>57885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471264</v>
+        <v>471304</v>
       </c>
       <c r="R13" t="n">
-        <v>6543968</v>
+        <v>6544023</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>131338964</v>
       </c>
       <c r="B8" t="n">
-        <v>57079</v>
+        <v>57082</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131338884</v>
+        <v>131339035</v>
       </c>
       <c r="B11" t="n">
-        <v>57076</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471264</v>
+        <v>471304</v>
       </c>
       <c r="R11" t="n">
-        <v>6543968</v>
+        <v>6544023</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,38 +1837,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131337775</v>
+        <v>131338884</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471285</v>
+        <v>471264</v>
       </c>
       <c r="R12" t="n">
-        <v>6543973</v>
+        <v>6543968</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131339035</v>
+        <v>131337775</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471304</v>
+        <v>471285</v>
       </c>
       <c r="R13" t="n">
-        <v>6544023</v>
+        <v>6543973</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>131337729</v>
       </c>
       <c r="B14" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>131444818</v>
       </c>
       <c r="B15" t="n">
-        <v>8440</v>
+        <v>8442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131444592</v>
       </c>
       <c r="B16" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>131338964</v>
       </c>
       <c r="B8" t="n">
-        <v>57082</v>
+        <v>57083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131339035</v>
+        <v>131338884</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471304</v>
+        <v>471264</v>
       </c>
       <c r="R11" t="n">
-        <v>6544023</v>
+        <v>6543968</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,38 +1837,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131338884</v>
+        <v>131337775</v>
       </c>
       <c r="B12" t="n">
-        <v>57079</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471264</v>
+        <v>471285</v>
       </c>
       <c r="R12" t="n">
-        <v>6543968</v>
+        <v>6543973</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R13" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>131337729</v>
       </c>
       <c r="B14" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131444592</v>
       </c>
       <c r="B16" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>131338964</v>
       </c>
       <c r="B8" t="n">
-        <v>57083</v>
+        <v>57089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131338884</v>
+        <v>131337775</v>
       </c>
       <c r="B11" t="n">
-        <v>57080</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471264</v>
+        <v>471285</v>
       </c>
       <c r="R11" t="n">
-        <v>6543968</v>
+        <v>6543973</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R12" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131339035</v>
+        <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57889</v>
+        <v>57086</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471304</v>
+        <v>471264</v>
       </c>
       <c r="R13" t="n">
-        <v>6544023</v>
+        <v>6543968</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>131337729</v>
       </c>
       <c r="B14" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131444592</v>
       </c>
       <c r="B16" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131339176</v>
+        <v>131338393</v>
       </c>
       <c r="B9" t="n">
         <v>57895</v>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471314</v>
+        <v>471301</v>
       </c>
       <c r="R9" t="n">
-        <v>6544075</v>
+        <v>6543890</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av döende gran.</t>
+          <t>Färska födohack vid basen på död stående tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,7 +1603,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131338393</v>
+        <v>131339176</v>
       </c>
       <c r="B10" t="n">
         <v>57895</v>
@@ -1639,14 +1639,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471301</v>
+        <v>471314</v>
       </c>
       <c r="R10" t="n">
-        <v>6543890</v>
+        <v>6544075</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen på död stående tall</t>
+          <t>Färska födohack vid basen av döende gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131338393</v>
+        <v>131339176</v>
       </c>
       <c r="B9" t="n">
         <v>57895</v>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471301</v>
+        <v>471314</v>
       </c>
       <c r="R9" t="n">
-        <v>6543890</v>
+        <v>6544075</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen på död stående tall</t>
+          <t>Färska födohack vid basen av döende gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,7 +1603,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131339176</v>
+        <v>131338393</v>
       </c>
       <c r="B10" t="n">
         <v>57895</v>
@@ -1639,14 +1639,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471314</v>
+        <v>471301</v>
       </c>
       <c r="R10" t="n">
-        <v>6544075</v>
+        <v>6543890</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av döende gran.</t>
+          <t>Färska födohack vid basen på död stående tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B11" t="n">
         <v>57895</v>
@@ -1751,7 +1751,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R11" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,7 +1837,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131339035</v>
+        <v>131337775</v>
       </c>
       <c r="B12" t="n">
         <v>57895</v>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471304</v>
+        <v>471285</v>
       </c>
       <c r="R12" t="n">
-        <v>6544023</v>
+        <v>6543973</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>131338050</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>131338964</v>
       </c>
       <c r="B8" t="n">
-        <v>57089</v>
+        <v>57090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131339035</v>
+        <v>131338884</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471304</v>
+        <v>471264</v>
       </c>
       <c r="R11" t="n">
-        <v>6544023</v>
+        <v>6543968</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,7 +1840,7 @@
         <v>131337775</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131338884</v>
+        <v>131339035</v>
       </c>
       <c r="B13" t="n">
-        <v>57086</v>
+        <v>57896</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471264</v>
+        <v>471304</v>
       </c>
       <c r="R13" t="n">
-        <v>6543968</v>
+        <v>6544023</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>131337729</v>
       </c>
       <c r="B14" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>131444818</v>
       </c>
       <c r="B15" t="n">
-        <v>8442</v>
+        <v>8443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131444592</v>
       </c>
       <c r="B16" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>131338964</v>
       </c>
       <c r="B8" t="n">
-        <v>57090</v>
+        <v>57093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131338884</v>
+        <v>131337775</v>
       </c>
       <c r="B11" t="n">
-        <v>57087</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471264</v>
+        <v>471285</v>
       </c>
       <c r="R11" t="n">
-        <v>6543968</v>
+        <v>6543973</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R12" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131339035</v>
+        <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57896</v>
+        <v>57090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471304</v>
+        <v>471264</v>
       </c>
       <c r="R13" t="n">
-        <v>6544023</v>
+        <v>6543968</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>131337729</v>
       </c>
       <c r="B14" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131444592</v>
       </c>
       <c r="B16" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131337775</v>
+        <v>131338884</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471285</v>
+        <v>471264</v>
       </c>
       <c r="R11" t="n">
-        <v>6543973</v>
+        <v>6543968</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,7 +1837,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131339035</v>
+        <v>131337775</v>
       </c>
       <c r="B12" t="n">
         <v>57899</v>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471304</v>
+        <v>471285</v>
       </c>
       <c r="R12" t="n">
-        <v>6544023</v>
+        <v>6543973</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131338884</v>
+        <v>131339035</v>
       </c>
       <c r="B13" t="n">
-        <v>57090</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471264</v>
+        <v>471304</v>
       </c>
       <c r="R13" t="n">
-        <v>6543968</v>
+        <v>6544023</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1720,38 +1720,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131338884</v>
+        <v>131337775</v>
       </c>
       <c r="B11" t="n">
-        <v>57090</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471264</v>
+        <v>471285</v>
       </c>
       <c r="R11" t="n">
-        <v>6543968</v>
+        <v>6543973</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,7 +1837,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131337775</v>
+        <v>131339035</v>
       </c>
       <c r="B12" t="n">
         <v>57899</v>
@@ -1868,7 +1868,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471285</v>
+        <v>471304</v>
       </c>
       <c r="R12" t="n">
-        <v>6543973</v>
+        <v>6544023</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,38 +1954,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131339035</v>
+        <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471304</v>
+        <v>471264</v>
       </c>
       <c r="R13" t="n">
-        <v>6544023</v>
+        <v>6543968</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>131338964</v>
       </c>
       <c r="B8" t="n">
-        <v>57093</v>
+        <v>57095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131339176</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131338393</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>131337775</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>131339035</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>131337729</v>
       </c>
       <c r="B14" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131444592</v>
       </c>
       <c r="B16" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -2186,7 +2186,7 @@
         <v>131444818</v>
       </c>
       <c r="B15" t="n">
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131444592</v>
       </c>
       <c r="B16" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -2298,7 +2298,7 @@
         <v>131444592</v>
       </c>
       <c r="B16" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122193935</v>
+        <v>129486827</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471285</v>
+        <v>471288</v>
       </c>
       <c r="R2" t="n">
-        <v>6544230</v>
+        <v>6544011</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -749,22 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4 st f.k</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,26 +780,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129486827</v>
+        <v>129487544</v>
       </c>
       <c r="B3" t="n">
-        <v>92881</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471288</v>
+        <v>471291</v>
       </c>
       <c r="R3" t="n">
-        <v>6544011</v>
+        <v>6544233</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -866,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4 st f.k</t>
+          <t>14 st f.k</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129487544</v>
+        <v>131337775</v>
       </c>
       <c r="B4" t="n">
-        <v>92881</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,39 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471291</v>
+        <v>471285</v>
       </c>
       <c r="R4" t="n">
-        <v>6544233</v>
+        <v>6543973</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,27 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>14 st f.k</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129572834</v>
+        <v>131338393</v>
       </c>
       <c r="B5" t="n">
-        <v>56930</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,27 +1037,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471271</v>
+        <v>471301</v>
       </c>
       <c r="R5" t="n">
-        <v>6544243</v>
+        <v>6543890</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1095,22 +1096,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen på död stående tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,12 +1131,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1140,11 +1146,11 @@
         <v>131338442</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1254,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131338050</v>
+        <v>131339035</v>
       </c>
       <c r="B7" t="n">
-        <v>5178</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471297</v>
+        <v>471304</v>
       </c>
       <c r="R7" t="n">
-        <v>6543926</v>
+        <v>6544023</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1324,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gnag och kläckhål på stående död gran</t>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131338964</v>
+        <v>131339176</v>
       </c>
       <c r="B8" t="n">
-        <v>57095</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,16 +1388,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1394,28 +1405,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471288</v>
+        <v>471314</v>
       </c>
       <c r="R8" t="n">
-        <v>6544000</v>
+        <v>6544075</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Skrämdes upp och flög nordväst.</t>
+          <t>Färska födohack vid basen av döende gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,14 +1494,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131339176</v>
+        <v>131445377</v>
       </c>
       <c r="B9" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1517,7 +1525,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471314</v>
+        <v>471350</v>
       </c>
       <c r="R9" t="n">
-        <v>6544075</v>
+        <v>6544009</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1556,27 +1564,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av döende gran.</t>
+          <t>Äldre födohack på stående död avbruten gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,38 +1611,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131338393</v>
+        <v>122193935</v>
       </c>
       <c r="B10" t="n">
-        <v>57901</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1643,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471301</v>
+        <v>471285</v>
       </c>
       <c r="R10" t="n">
-        <v>6543890</v>
+        <v>6544230</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1673,27 +1685,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen på död stående tall</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,50 +1715,50 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131337775</v>
+        <v>129572834</v>
       </c>
       <c r="B11" t="n">
-        <v>57901</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1760,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471285</v>
+        <v>471271</v>
       </c>
       <c r="R11" t="n">
-        <v>6543973</v>
+        <v>6544243</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1790,27 +1797,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,50 +1827,50 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131339035</v>
+        <v>131337729</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1879,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471304</v>
+        <v>471298</v>
       </c>
       <c r="R12" t="n">
-        <v>6544023</v>
+        <v>6543979</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1912,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1954,7 @@
         <v>131338884</v>
       </c>
       <c r="B13" t="n">
-        <v>57092</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131337729</v>
+        <v>131444592</v>
       </c>
       <c r="B14" t="n">
-        <v>57092</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,19 +2099,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471298</v>
+        <v>471273</v>
       </c>
       <c r="R14" t="n">
-        <v>6543979</v>
+        <v>6544232</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2141,22 +2138,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131444818</v>
+        <v>131338050</v>
       </c>
       <c r="B15" t="n">
-        <v>8444</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,21 +2191,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,10 +2215,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471258</v>
+        <v>471297</v>
       </c>
       <c r="R15" t="n">
-        <v>6544133</v>
+        <v>6543926</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2248,27 +2245,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre gnag på låga av björk.</t>
+          <t>Gnag och kläckhål på stående död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131444592</v>
+        <v>131338964</v>
       </c>
       <c r="B16" t="n">
-        <v>57100</v>
+        <v>57144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,42 +2303,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471273</v>
+        <v>471288</v>
       </c>
       <c r="R16" t="n">
-        <v>6544232</v>
+        <v>6544000</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2365,22 +2365,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Skrämdes upp och flög nordväst.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,6 +2409,454 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131444353</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>471307</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6544283</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre gnag</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131444376</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6544280</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre gnag</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131444818</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>471258</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6544133</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre gnag på låga av björk.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131445502</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6544098</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2180,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131338050</v>
+        <v>134515804</v>
       </c>
       <c r="B15" t="n">
-        <v>5179</v>
+        <v>57162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,34 +2191,53 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471297</v>
+        <v>471258</v>
       </c>
       <c r="R15" t="n">
-        <v>6543926</v>
+        <v>6544237</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2245,27 +2264,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gnag och kläckhål på stående död gran</t>
+          <t>Färsk fjäderpenna fr vingen på tjädertupp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2311,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131338964</v>
+        <v>131338050</v>
       </c>
       <c r="B16" t="n">
-        <v>57144</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,45 +2322,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102613</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471288</v>
+        <v>471297</v>
       </c>
       <c r="R16" t="n">
-        <v>6544000</v>
+        <v>6543926</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2370,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,12 +2391,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Skrämdes upp och flög nordväst.</t>
+          <t>Gnag och kläckhål på stående död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2412,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131444353</v>
+        <v>131338964</v>
       </c>
       <c r="B17" t="n">
-        <v>8444</v>
+        <v>57144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,37 +2434,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471307</v>
+        <v>471288</v>
       </c>
       <c r="R17" t="n">
-        <v>6544283</v>
+        <v>6544000</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,27 +2496,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre gnag</t>
+          <t>Skrämdes upp och flög nordväst.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,7 +2543,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131444376</v>
+        <v>131444353</v>
       </c>
       <c r="B18" t="n">
         <v>8444</v>
@@ -2559,10 +2578,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471316</v>
+        <v>471307</v>
       </c>
       <c r="R18" t="n">
-        <v>6544280</v>
+        <v>6544283</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2594,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2636,7 +2655,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131444818</v>
+        <v>131444376</v>
       </c>
       <c r="B19" t="n">
         <v>8444</v>
@@ -2671,10 +2690,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471258</v>
+        <v>471316</v>
       </c>
       <c r="R19" t="n">
-        <v>6544133</v>
+        <v>6544280</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2706,7 +2725,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,12 +2735,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre gnag på låga av björk.</t>
+          <t>Äldre gnag</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,7 +2767,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131445502</v>
+        <v>131444818</v>
       </c>
       <c r="B20" t="n">
         <v>8444</v>
@@ -2783,10 +2802,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471316</v>
+        <v>471258</v>
       </c>
       <c r="R20" t="n">
-        <v>6544098</v>
+        <v>6544133</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2818,7 +2837,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,12 +2847,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre kläckhål.</t>
+          <t>Äldre gnag på låga av björk.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2857,6 +2876,118 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131445502</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6544098</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129486827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487544</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131337775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131338393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131338442</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131339035</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1491,6 +1526,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131339176</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131445377</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1724,6 +1769,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122193935</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +1886,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129572834</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131337729</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2065,6 +2125,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131338884</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2177,6 +2242,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444592</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2308,6 +2378,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134515804</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2420,6 +2495,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131338050</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2540,6 +2620,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131338964</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2652,6 +2737,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444353</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2764,6 +2854,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444376</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2876,6 +2971,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444818</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2988,8 +3088,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131445502</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2386,10 +2386,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131338050</v>
+        <v>135602701</v>
       </c>
       <c r="B16" t="n">
-        <v>5179</v>
+        <v>57162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,37 +2397,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471297</v>
+        <v>471283</v>
       </c>
       <c r="R16" t="n">
-        <v>6543926</v>
+        <v>6543985</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2451,27 +2460,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gnag och kläckhål på stående död gran</t>
+          <t>Fjädrar och spillning fr höna.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,16 +2506,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338050</t>
+          <t>https://artportalen.se/Sighting/135602701</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131338964</v>
+        <v>135602702</v>
       </c>
       <c r="B17" t="n">
-        <v>57144</v>
+        <v>57162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,21 +2523,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2536,23 +2545,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471288</v>
+        <v>471283</v>
       </c>
       <c r="R17" t="n">
-        <v>6544000</v>
+        <v>6543974</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,27 +2586,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Skrämdes upp och flög nordväst.</t>
+          <t>Färska fjädrar och spillning fr höna</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2622,16 +2632,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338964</t>
+          <t>https://artportalen.se/Sighting/135602702</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131444353</v>
+        <v>135602704</v>
       </c>
       <c r="B18" t="n">
-        <v>8444</v>
+        <v>57162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,37 +2649,52 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471307</v>
+        <v>471359</v>
       </c>
       <c r="R18" t="n">
-        <v>6544283</v>
+        <v>6543969</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2693,27 +2718,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre gnag</t>
+          <t>Färsk fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,16 +2764,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444353</t>
+          <t>https://artportalen.se/Sighting/135602704</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131444376</v>
+        <v>131338050</v>
       </c>
       <c r="B19" t="n">
-        <v>8444</v>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,21 +2781,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2780,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471316</v>
+        <v>471297</v>
       </c>
       <c r="R19" t="n">
-        <v>6544280</v>
+        <v>6543926</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2810,27 +2835,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre gnag</t>
+          <t>Gnag och kläckhål på stående död gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2856,16 +2881,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444376</t>
+          <t>https://artportalen.se/Sighting/131338050</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131444818</v>
+        <v>131338964</v>
       </c>
       <c r="B20" t="n">
-        <v>8444</v>
+        <v>57144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2873,37 +2898,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>102613</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471258</v>
+        <v>471288</v>
       </c>
       <c r="R20" t="n">
-        <v>6544133</v>
+        <v>6544000</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2927,27 +2960,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre gnag på låga av björk.</t>
+          <t>Skrämdes upp och flög nordväst.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2973,13 +3006,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444818</t>
+          <t>https://artportalen.se/Sighting/131338964</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131445502</v>
+        <v>131444353</v>
       </c>
       <c r="B21" t="n">
         <v>8444</v>
@@ -3014,10 +3047,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471316</v>
+        <v>471307</v>
       </c>
       <c r="R21" t="n">
-        <v>6544098</v>
+        <v>6544283</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3049,7 +3082,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3059,12 +3092,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre kläckhål.</t>
+          <t>Äldre gnag</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3089,6 +3122,357 @@
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444353</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131444376</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6544280</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre gnag</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444376</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131444818</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>471258</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6544133</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre gnag på låga av björk.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444818</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131445502</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6544098</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131445502</t>
         </is>
@@ -3116,6 +3500,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -2389,7 +2389,7 @@
         <v>135602701</v>
       </c>
       <c r="B16" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>135602702</v>
       </c>
       <c r="B17" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>135602704</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2386,10 +2386,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131338050</v>
+        <v>135602701</v>
       </c>
       <c r="B16" t="n">
-        <v>5179</v>
+        <v>57167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,37 +2397,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471297</v>
+        <v>471283</v>
       </c>
       <c r="R16" t="n">
-        <v>6543926</v>
+        <v>6543985</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2451,27 +2460,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gnag och kläckhål på stående död gran</t>
+          <t>Fjädrar och spillning fr höna.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,16 +2506,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338050</t>
+          <t>https://artportalen.se/Sighting/135602701</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131338964</v>
+        <v>135602702</v>
       </c>
       <c r="B17" t="n">
-        <v>57144</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,21 +2523,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2536,23 +2545,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471288</v>
+        <v>471283</v>
       </c>
       <c r="R17" t="n">
-        <v>6544000</v>
+        <v>6543974</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,27 +2586,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Skrämdes upp och flög nordväst.</t>
+          <t>Färska fjädrar och spillning fr höna</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2622,16 +2632,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338964</t>
+          <t>https://artportalen.se/Sighting/135602702</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131444353</v>
+        <v>135602704</v>
       </c>
       <c r="B18" t="n">
-        <v>8444</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,37 +2649,52 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471307</v>
+        <v>471359</v>
       </c>
       <c r="R18" t="n">
-        <v>6544283</v>
+        <v>6543969</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2693,27 +2718,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre gnag</t>
+          <t>Färsk fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,16 +2764,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444353</t>
+          <t>https://artportalen.se/Sighting/135602704</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131444376</v>
+        <v>131338050</v>
       </c>
       <c r="B19" t="n">
-        <v>8444</v>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,21 +2781,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2780,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471316</v>
+        <v>471297</v>
       </c>
       <c r="R19" t="n">
-        <v>6544280</v>
+        <v>6543926</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2810,27 +2835,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre gnag</t>
+          <t>Gnag och kläckhål på stående död gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2856,16 +2881,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444376</t>
+          <t>https://artportalen.se/Sighting/131338050</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131444818</v>
+        <v>131338964</v>
       </c>
       <c r="B20" t="n">
-        <v>8444</v>
+        <v>57144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2873,37 +2898,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>102613</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471258</v>
+        <v>471288</v>
       </c>
       <c r="R20" t="n">
-        <v>6544133</v>
+        <v>6544000</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2927,27 +2960,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre gnag på låga av björk.</t>
+          <t>Skrämdes upp och flög nordväst.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2973,13 +3006,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444818</t>
+          <t>https://artportalen.se/Sighting/131338964</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131445502</v>
+        <v>131444353</v>
       </c>
       <c r="B21" t="n">
         <v>8444</v>
@@ -3014,10 +3047,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471316</v>
+        <v>471307</v>
       </c>
       <c r="R21" t="n">
-        <v>6544098</v>
+        <v>6544283</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3049,7 +3082,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3059,12 +3092,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre kläckhål.</t>
+          <t>Äldre gnag</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3089,6 +3122,357 @@
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444353</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131444376</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6544280</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre gnag</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444376</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131444818</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>471258</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6544133</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre gnag på låga av björk.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444818</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131445502</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6544098</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131445502</t>
         </is>
@@ -3116,6 +3500,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -2389,7 +2389,7 @@
         <v>135602701</v>
       </c>
       <c r="B16" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>135602702</v>
       </c>
       <c r="B17" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>135602704</v>
       </c>
       <c r="B18" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,27 +924,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131337775</v>
+        <v>136304863</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,21 +953,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Diamanten, Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471285</v>
+        <v>471295</v>
       </c>
       <c r="R4" t="n">
-        <v>6543973</v>
+        <v>6543907</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -994,27 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,33 +1035,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131337775</t>
+          <t>https://artportalen.se/Sighting/136304863</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131338393</v>
+        <v>136305330</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>57908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1075,21 +1070,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471301</v>
+        <v>471258</v>
       </c>
       <c r="R5" t="n">
-        <v>6543890</v>
+        <v>6544185</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1116,27 +1111,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen på död stående tall</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,33 +1152,33 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338393</t>
+          <t>https://artportalen.se/Sighting/136305330</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131338442</v>
+        <v>136305493</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>57908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1197,21 +1187,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Diamanten, Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471280</v>
+        <v>471279</v>
       </c>
       <c r="R6" t="n">
-        <v>6543893</v>
+        <v>6543946</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1238,27 +1228,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre födohack vid basen på lutande död tall</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,33 +1269,33 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338442</t>
+          <t>https://artportalen.se/Sighting/136305493</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131339035</v>
+        <v>136305638</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1319,21 +1304,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Diamanten, Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471304</v>
+        <v>471293</v>
       </c>
       <c r="R7" t="n">
-        <v>6544023</v>
+        <v>6543914</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1360,27 +1345,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre födohack vid basen av död stående tall</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,13 +1386,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131339035</t>
+          <t>https://artportalen.se/Sighting/136305638</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131339176</v>
+        <v>131337775</v>
       </c>
       <c r="B8" t="n">
         <v>57950</v>
@@ -1448,14 +1428,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471314</v>
+        <v>471285</v>
       </c>
       <c r="R8" t="n">
-        <v>6544075</v>
+        <v>6543973</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1487,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1477,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av döende gran.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,13 +1508,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131339176</t>
+          <t>https://artportalen.se/Sighting/131337775</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131445377</v>
+        <v>131338393</v>
       </c>
       <c r="B9" t="n">
         <v>57950</v>
@@ -1565,19 +1545,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471350</v>
+        <v>471301</v>
       </c>
       <c r="R9" t="n">
-        <v>6544009</v>
+        <v>6543890</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1604,27 +1584,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre födohack på stående död avbruten gran</t>
+          <t>Färska födohack vid basen på död stående tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,16 +1630,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131445377</t>
+          <t>https://artportalen.se/Sighting/131338393</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122193935</v>
+        <v>131338442</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,31 +1647,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1700,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471285</v>
+        <v>471280</v>
       </c>
       <c r="R10" t="n">
-        <v>6544230</v>
+        <v>6543893</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1730,22 +1706,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre födohack vid basen på lutande död tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,27 +1741,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122193935</t>
+          <t>https://artportalen.se/Sighting/131338442</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129572834</v>
+        <v>131339035</v>
       </c>
       <c r="B11" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,27 +1769,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1817,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471271</v>
+        <v>471304</v>
       </c>
       <c r="R11" t="n">
-        <v>6544243</v>
+        <v>6544023</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1847,22 +1828,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre födohack vid basen av död stående tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,27 +1863,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129572834</t>
+          <t>https://artportalen.se/Sighting/131339035</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131337729</v>
+        <v>131339176</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,39 +1891,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471298</v>
+        <v>471314</v>
       </c>
       <c r="R12" t="n">
-        <v>6543979</v>
+        <v>6544075</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1969,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1979,7 +1965,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av döende gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2005,16 +1996,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131337729</t>
+          <t>https://artportalen.se/Sighting/131339176</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131338884</v>
+        <v>131445377</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,39 +2013,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471264</v>
+        <v>471350</v>
       </c>
       <c r="R13" t="n">
-        <v>6543968</v>
+        <v>6544009</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2081,27 +2072,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På 2 stenar.</t>
+          <t>Äldre födohack på stående död avbruten gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,13 +2118,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338884</t>
+          <t>https://artportalen.se/Sighting/131445377</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131444592</v>
+        <v>122193935</v>
       </c>
       <c r="B14" t="n">
         <v>57141</v>
@@ -2161,22 +2152,26 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471273</v>
+        <v>471285</v>
       </c>
       <c r="R14" t="n">
-        <v>6544232</v>
+        <v>6544230</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2203,22 +2198,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2233,27 +2228,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444592</t>
+          <t>https://artportalen.se/Sighting/122193935</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134515804</v>
+        <v>129572834</v>
       </c>
       <c r="B15" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2278,36 +2273,22 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>hane</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471258</v>
+        <v>471271</v>
       </c>
       <c r="R15" t="n">
-        <v>6544237</v>
+        <v>6544243</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2334,27 +2315,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färsk fjäderpenna fr vingen på tjädertupp.</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,27 +2345,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134515804</t>
+          <t>https://artportalen.se/Sighting/129572834</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135602701</v>
+        <v>131337729</v>
       </c>
       <c r="B16" t="n">
-        <v>57169</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,29 +2390,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Diamanten, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471283</v>
+        <v>471298</v>
       </c>
       <c r="R16" t="n">
-        <v>6543985</v>
+        <v>6543979</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2460,27 +2432,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjädrar och spillning fr höna.</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,16 +2473,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602701</t>
+          <t>https://artportalen.se/Sighting/131337729</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135602702</v>
+        <v>131338884</v>
       </c>
       <c r="B17" t="n">
-        <v>57169</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,29 +2507,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Diamanten, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471283</v>
+        <v>471264</v>
       </c>
       <c r="R17" t="n">
-        <v>6543974</v>
+        <v>6543968</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2586,27 +2549,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska fjädrar och spillning fr höna</t>
+          <t>På 2 stenar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2632,16 +2595,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602702</t>
+          <t>https://artportalen.se/Sighting/131338884</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135602704</v>
+        <v>131444592</v>
       </c>
       <c r="B18" t="n">
-        <v>57169</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,34 +2630,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Diamanten, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471359</v>
+        <v>471273</v>
       </c>
       <c r="R18" t="n">
-        <v>6543969</v>
+        <v>6544232</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2718,27 +2671,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färsk fjäder fr tupp</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,16 +2712,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602704</t>
+          <t>https://artportalen.se/Sighting/131444592</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131338050</v>
+        <v>134515804</v>
       </c>
       <c r="B19" t="n">
-        <v>5179</v>
+        <v>57162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,34 +2729,53 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471297</v>
+        <v>471258</v>
       </c>
       <c r="R19" t="n">
-        <v>6543926</v>
+        <v>6544237</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2835,27 +2802,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gnag och kläckhål på stående död gran</t>
+          <t>Färsk fjäderpenna fr vingen på tjädertupp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,16 +2848,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338050</t>
+          <t>https://artportalen.se/Sighting/134515804</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131338964</v>
+        <v>135602701</v>
       </c>
       <c r="B20" t="n">
-        <v>57144</v>
+        <v>57169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2898,21 +2865,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2920,23 +2887,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471288</v>
+        <v>471283</v>
       </c>
       <c r="R20" t="n">
-        <v>6544000</v>
+        <v>6543985</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2960,27 +2928,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Skrämdes upp och flög nordväst.</t>
+          <t>Fjädrar och spillning fr höna.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3006,16 +2974,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131338964</t>
+          <t>https://artportalen.se/Sighting/135602701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131444353</v>
+        <v>135602702</v>
       </c>
       <c r="B21" t="n">
-        <v>8444</v>
+        <v>57169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,37 +2991,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471307</v>
+        <v>471283</v>
       </c>
       <c r="R21" t="n">
-        <v>6544283</v>
+        <v>6543974</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3077,27 +3054,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre gnag</t>
+          <t>Färska fjädrar och spillning fr höna</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3123,16 +3100,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444353</t>
+          <t>https://artportalen.se/Sighting/135602702</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131444376</v>
+        <v>135602704</v>
       </c>
       <c r="B22" t="n">
-        <v>8444</v>
+        <v>57169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,37 +3117,52 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>Diamanten, Nrk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471316</v>
+        <v>471359</v>
       </c>
       <c r="R22" t="n">
-        <v>6544280</v>
+        <v>6543969</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3194,27 +3186,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre gnag</t>
+          <t>Färsk fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3240,16 +3232,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444376</t>
+          <t>https://artportalen.se/Sighting/135602704</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131444818</v>
+        <v>131338050</v>
       </c>
       <c r="B23" t="n">
-        <v>8444</v>
+        <v>5179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,21 +3249,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3281,10 +3273,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471258</v>
+        <v>471297</v>
       </c>
       <c r="R23" t="n">
-        <v>6544133</v>
+        <v>6543926</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3311,27 +3303,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre gnag på låga av björk.</t>
+          <t>Gnag och kläckhål på stående död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3357,16 +3349,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131444818</t>
+          <t>https://artportalen.se/Sighting/131338050</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131445502</v>
+        <v>131338964</v>
       </c>
       <c r="B24" t="n">
-        <v>8444</v>
+        <v>57144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3374,37 +3366,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>102613</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471316</v>
+        <v>471288</v>
       </c>
       <c r="R24" t="n">
-        <v>6544098</v>
+        <v>6544000</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3428,27 +3428,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre kläckhål.</t>
+          <t>Skrämdes upp och flög nordväst.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3473,6 +3473,1059 @@
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131338964</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136304930</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58146</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Diamanten, Diamanten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>471295</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6543907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136304930</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136304982</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58148</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Diamanten, Diamanten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>471295</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6543907</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136304982</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136305478</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Diamanten, Diamanten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>471279</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6543946</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136305478</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136305601</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58148</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Diamanten, Diamanten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>471293</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6543914</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136305601</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136305405</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>471258</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6544185</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136305405</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131444353</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>471307</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6544283</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre gnag</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444353</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131444376</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6544280</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre gnag</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444376</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131444818</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>471258</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6544133</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre gnag på låga av björk.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131444818</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131445502</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6544098</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131445502</t>
         </is>
@@ -3503,6 +4556,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136304863</v>
       </c>
       <c r="B4" t="n">
-        <v>57908</v>
+        <v>57909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136305330</v>
       </c>
       <c r="B5" t="n">
-        <v>57908</v>
+        <v>57909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136305493</v>
       </c>
       <c r="B6" t="n">
-        <v>57908</v>
+        <v>57909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136305638</v>
       </c>
       <c r="B7" t="n">
-        <v>57908</v>
+        <v>57909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136304930</v>
       </c>
       <c r="B25" t="n">
-        <v>58146</v>
+        <v>58147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136304982</v>
       </c>
       <c r="B26" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>136305478</v>
       </c>
       <c r="B27" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136305601</v>
       </c>
       <c r="B28" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136305405</v>
       </c>
       <c r="B29" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
